--- a/reports/downloads/bbm_diffusion.xlsx
+++ b/reports/downloads/bbm_diffusion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9018"/>
+  <dimension ref="A1:B9041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72568,6 +72568,190 @@
         <v>27</v>
       </c>
     </row>
+    <row r="9019">
+      <c r="A9019" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B9019" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9020">
+      <c r="A9020" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B9020" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9021">
+      <c r="A9021" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B9021" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9022">
+      <c r="A9022" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B9022" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9023">
+      <c r="A9023" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B9023" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9024">
+      <c r="A9024" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B9024" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9025">
+      <c r="A9025" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B9025" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9026">
+      <c r="A9026" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B9026" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9027">
+      <c r="A9027" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B9027" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9028">
+      <c r="A9028" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B9028" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9029">
+      <c r="A9029" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B9029" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9030">
+      <c r="A9030" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B9030" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9031">
+      <c r="A9031" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B9031" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9032">
+      <c r="A9032" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B9032" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9033">
+      <c r="A9033" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B9033" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9034">
+      <c r="A9034" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B9034" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9035">
+      <c r="A9035" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B9035" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9036">
+      <c r="A9036" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B9036" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9037">
+      <c r="A9037" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B9037" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9038">
+      <c r="A9038" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B9038" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9039">
+      <c r="A9039" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9039" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9040">
+      <c r="A9040" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B9040" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9041">
+      <c r="A9041" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B9041" t="n">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
